--- a/Presupuestos.xlsx
+++ b/Presupuestos.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCBB515-6329-43A7-9D0C-CE2774088C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F2BF86-E291-42AA-A124-757909A7DCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9481DF28-0B3E-48A4-9B25-BB3654989BFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$P$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$3:$P$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="48">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -60,9 +60,6 @@
     <t>ASISTIDOR</t>
   </si>
   <si>
-    <t xml:space="preserve"> GOLEADOR</t>
-  </si>
-  <si>
     <t>PRETEMPORADA</t>
   </si>
   <si>
@@ -126,30 +123,9 @@
     <t>Arsenal</t>
   </si>
   <si>
-    <t>Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>Hellas Verona</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
     <t>Wrexham</t>
   </si>
   <si>
-    <t>CAMPEON</t>
-  </si>
-  <si>
-    <t>SUBCAMPEON</t>
-  </si>
-  <si>
-    <t>SEMIFINAL</t>
-  </si>
-  <si>
-    <t>CUARTOS</t>
-  </si>
-  <si>
     <t>Atletico de Madrid</t>
   </si>
   <si>
@@ -196,6 +172,21 @@
   </si>
   <si>
     <t>eliot anderson -&gt; como x 50 M 1 temp</t>
+  </si>
+  <si>
+    <t>8vos</t>
+  </si>
+  <si>
+    <t>4tos</t>
+  </si>
+  <si>
+    <t>Semis</t>
+  </si>
+  <si>
+    <t>GOLEADOR/ASISTIDOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GOLEADOR/ASISTIDOR</t>
   </si>
 </sst>
 </file>
@@ -263,7 +254,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -286,56 +277,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -368,22 +319,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -725,187 +668,156 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08C8DD9-62BF-4F61-8FBF-6664D0041D04}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="23.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.109375" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="17" t="s">
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="14"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="6"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="7"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
-        <v>320</v>
-      </c>
-      <c r="D3" s="2">
-        <v>105</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="4">
-        <v>320</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="6">
-        <v>20</v>
-      </c>
-      <c r="M3" s="1">
-        <v>1732</v>
-      </c>
-      <c r="N3" s="1">
-        <f>C3+D3+E3+G3+H3+J3+K3+L3</f>
-        <v>765</v>
-      </c>
-      <c r="O3" s="1"/>
-      <c r="P3" s="7">
-        <f t="shared" ref="P3:P11" si="0">M3+N3-O3</f>
-        <v>2497</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="D4" s="2">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2">
-        <v>140</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="4">
-        <v>170</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="5">
-        <v>200</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="6">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="3">
+        <v>50</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="5">
+        <v>20</v>
       </c>
       <c r="M4" s="1">
-        <v>106</v>
+        <v>1732</v>
       </c>
       <c r="N4" s="1">
-        <f t="shared" ref="N4:N18" si="1">C4+D4+E4+G4+H4+J4+K4+L4</f>
-        <v>915</v>
+        <f>C4+D4+E4+G4+H4+J4+K4+L4</f>
+        <v>465</v>
       </c>
       <c r="O4" s="1"/>
-      <c r="P4" s="7">
-        <f t="shared" si="0"/>
-        <v>1021</v>
+      <c r="P4" s="6">
+        <f>M4+N4-O4</f>
+        <v>2197</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -913,117 +825,121 @@
         <v>25</v>
       </c>
       <c r="B5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="D5" s="2">
+        <v>55</v>
+      </c>
+      <c r="E5" s="2">
+        <v>127</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="3">
         <v>50</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="4">
-        <v>100</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="5">
-        <v>250</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="6">
-        <v>10</v>
-      </c>
-      <c r="M5" s="1">
-        <v>433</v>
-      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="4">
+        <v>200</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="5">
+        <v>35</v>
+      </c>
+      <c r="M5" s="1"/>
       <c r="N5" s="1">
-        <f t="shared" si="1"/>
-        <v>690</v>
+        <f>C5+D5+E5+G5+H5+J5+K5+L5</f>
+        <v>777</v>
       </c>
       <c r="O5" s="1"/>
-      <c r="P5" s="7">
-        <f t="shared" si="0"/>
-        <v>1123</v>
+      <c r="P5" s="6">
+        <f>M5+N5-O5</f>
+        <v>777</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="D6" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="4">
-        <v>200</v>
-      </c>
-      <c r="H6" s="4">
-        <v>60</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5">
+      <c r="F6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="3">
         <v>100</v>
       </c>
-      <c r="L6" s="6">
-        <v>20</v>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="4">
+        <v>250</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5">
+        <v>5</v>
       </c>
       <c r="M6" s="1">
-        <v>1265</v>
+        <v>433</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" si="1"/>
-        <v>667</v>
+        <f>C6+D6+E6+G6+H6+J6+K6+L6</f>
+        <v>693</v>
       </c>
       <c r="O6" s="1"/>
-      <c r="P6" s="7">
-        <f t="shared" si="0"/>
-        <v>1932</v>
+      <c r="P6" s="6">
+        <f>M6+N6-O6</f>
+        <v>1126</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="2">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="1"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="5">
+        <v>10</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1265</v>
+      </c>
       <c r="N7" s="1">
-        <f t="shared" si="1"/>
-        <v>240</v>
+        <f>C7+D7+E7+G7+H7+J7+K7+L7</f>
+        <v>300</v>
       </c>
       <c r="O7" s="1"/>
-      <c r="P7" s="7">
-        <f t="shared" si="0"/>
-        <v>240</v>
+      <c r="P7" s="6">
+        <f>M7+N7-O7</f>
+        <v>1565</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -1031,157 +947,171 @@
         <v>18</v>
       </c>
       <c r="B8" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>220</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="D8" s="2">
+        <v>60</v>
+      </c>
       <c r="E8" s="2">
-        <v>65</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="4">
-        <v>170</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="5">
-        <v>250</v>
-      </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="6">
-        <v>20</v>
-      </c>
-      <c r="M8" s="1">
-        <v>2097</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="5">
+        <v>15</v>
+      </c>
+      <c r="M8" s="1"/>
       <c r="N8" s="1">
-        <f t="shared" si="1"/>
-        <v>725</v>
+        <f>C8+D8+E8+G8+H8+J8+K8+L8</f>
+        <v>553</v>
       </c>
       <c r="O8" s="1"/>
-      <c r="P8" s="7">
-        <f t="shared" si="0"/>
-        <v>2822</v>
+      <c r="P8" s="6">
+        <f>M8+N8-O8</f>
+        <v>553</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2">
+        <v>270</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2">
+        <v>40</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3">
+        <v>60</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="4">
         <v>200</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="4">
-        <v>100</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="6">
-        <v>20</v>
+      <c r="K9" s="4"/>
+      <c r="L9" s="5">
+        <v>15</v>
       </c>
       <c r="M9" s="1">
-        <v>205</v>
+        <v>2097</v>
       </c>
       <c r="N9" s="1">
-        <f t="shared" si="1"/>
-        <v>320</v>
+        <f>C9+D9+E9+G9+H9+J9+K9+L9</f>
+        <v>585</v>
       </c>
       <c r="O9" s="1"/>
-      <c r="P9" s="7">
-        <f t="shared" si="0"/>
-        <v>525</v>
+      <c r="P9" s="6">
+        <f>M9+N9-O9</f>
+        <v>2682</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="D10" s="2">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2">
+        <v>85</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="3">
         <v>50</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="5">
+      <c r="H10" s="3"/>
+      <c r="I10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="4">
         <v>200</v>
       </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="6"/>
+      <c r="K10" s="4">
+        <v>60</v>
+      </c>
+      <c r="L10" s="5">
+        <v>30</v>
+      </c>
       <c r="M10" s="1">
-        <v>251</v>
+        <v>191</v>
       </c>
       <c r="N10" s="1">
-        <f t="shared" si="1"/>
-        <v>535</v>
+        <f>C10+D10+E10+G10+H10+J10+K10+L10</f>
+        <v>755</v>
       </c>
       <c r="O10" s="1"/>
-      <c r="P10" s="7">
-        <f t="shared" si="0"/>
-        <v>786</v>
+      <c r="P10" s="6">
+        <f>M10+N10-O10</f>
+        <v>946</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2">
-        <v>160</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="D11" s="2">
+        <v>30</v>
+      </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="5">
-        <v>200</v>
-      </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6"/>
+      <c r="F11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="3">
+        <v>100</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5">
+        <v>45</v>
+      </c>
       <c r="M11" s="1">
-        <v>1259</v>
+        <v>921</v>
       </c>
       <c r="N11" s="1">
-        <f t="shared" si="1"/>
-        <v>360</v>
-      </c>
-      <c r="O11" s="1"/>
-      <c r="P11" s="7">
-        <f t="shared" si="0"/>
-        <v>1619</v>
+        <f>C11+D11+E11+G11+H11+J11+K11+L11</f>
+        <v>425</v>
+      </c>
+      <c r="O11" s="1">
+        <v>158</v>
+      </c>
+      <c r="P11" s="6">
+        <f>M11+N11-O11</f>
+        <v>1188</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -1189,236 +1119,330 @@
         <v>23</v>
       </c>
       <c r="B12" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2">
-        <v>140</v>
-      </c>
-      <c r="D12" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="D12" s="2">
+        <v>27</v>
+      </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="6">
-        <v>10</v>
+      <c r="F12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="3">
+        <v>100</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="5">
+        <v>45</v>
       </c>
       <c r="M12" s="1">
-        <v>921</v>
+        <v>205</v>
       </c>
       <c r="N12" s="1">
-        <f t="shared" si="1"/>
-        <v>150</v>
-      </c>
-      <c r="O12" s="1">
-        <v>158</v>
-      </c>
-      <c r="P12" s="7">
+        <f>C12+D12+E12+G12+H12+J12+K12+L12</f>
+        <v>412</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="6">
         <f>M12+N12-O12</f>
-        <v>913</v>
+        <v>617</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="2">
-        <v>120</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D13" s="2">
+        <v>40</v>
+      </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="F13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="3">
         <v>100</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="6">
-        <v>20</v>
-      </c>
-      <c r="M13" s="1">
-        <v>300</v>
-      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="1"/>
       <c r="N13" s="1">
-        <f t="shared" si="1"/>
-        <v>240</v>
+        <f>C13+D13+E13+G13+H13+J13+K13+L13</f>
+        <v>370</v>
       </c>
       <c r="O13" s="1"/>
-      <c r="P13" s="7">
-        <f t="shared" ref="P13:P18" si="2">M13+N13-O13</f>
-        <v>540</v>
+      <c r="P13" s="6">
+        <f>M13+N13-O13</f>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2">
-        <v>100</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2">
-        <v>45</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="6">
-        <v>10</v>
-      </c>
-      <c r="M14" s="1">
-        <v>191</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="D14" s="2">
+        <v>35</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="3">
+        <v>50</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="1"/>
       <c r="N14" s="1">
-        <f t="shared" si="1"/>
-        <v>155</v>
+        <f>C14+D14+E14+G14+H14+J14+K14+L14</f>
+        <v>305</v>
       </c>
       <c r="O14" s="1"/>
-      <c r="P14" s="7">
-        <f t="shared" si="2"/>
-        <v>346</v>
+      <c r="P14" s="6">
+        <f>M14+N14-O14</f>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>13</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="C15" s="2">
+        <v>210</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="1"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="4">
+        <v>250</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="5">
+        <v>15</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1259</v>
+      </c>
       <c r="N15" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C15+D15+E15+G15+H15+J15+K15+L15</f>
+        <v>475</v>
       </c>
       <c r="O15" s="1"/>
-      <c r="P15" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="P15" s="6">
+        <f>M15+N15-O15</f>
+        <v>1734</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="C16" s="2">
+        <v>200</v>
+      </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="6"/>
+      <c r="F16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="3">
+        <v>50</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="5">
+        <v>40</v>
+      </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C16+D16+E16+G16+H16+J16+K16+L16</f>
+        <v>290</v>
       </c>
       <c r="O16" s="1"/>
-      <c r="P16" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="P16" s="6">
+        <f>M16+N16-O16</f>
+        <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="C17" s="2">
+        <v>190</v>
+      </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J17" s="5">
-        <v>200</v>
-      </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="1"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="1">
+        <v>106</v>
+      </c>
       <c r="N17" s="1">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f>C17+D17+E17+G17+H17+J17+K17+L17</f>
+        <v>190</v>
       </c>
       <c r="O17" s="1"/>
-      <c r="P17" s="7">
-        <f t="shared" si="2"/>
-        <v>200</v>
+      <c r="P17" s="6">
+        <f>M17+N17-O17</f>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2">
-        <v>16</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="C18" s="2">
+        <v>180</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="1"/>
+      <c r="F18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="3">
+        <v>150</v>
+      </c>
+      <c r="H18" s="3">
+        <v>60</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4">
+        <v>60</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" s="1">
+        <v>251</v>
+      </c>
       <c r="N18" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C18+D18+E18+G18+H18+J18+K18+L18</f>
+        <v>450</v>
       </c>
       <c r="O18" s="1"/>
-      <c r="P18" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="P18" s="6">
+        <f>M18+N18-O18</f>
+        <v>701</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="2">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2">
+        <v>170</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="4">
+        <v>200</v>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="1">
+        <v>300</v>
+      </c>
+      <c r="N19" s="1">
+        <f>C19+D19+E19+G19+H19+J19+K19+L19</f>
+        <v>370</v>
+      </c>
+      <c r="O19" s="1"/>
+      <c r="P19" s="6">
+        <f>M19+N19-O19</f>
+        <v>670</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="3">
+        <v>50</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1">
+        <f>C20+D20+E20+G20+H20+J20+K20+L20</f>
+        <v>50</v>
+      </c>
+      <c r="O20" s="1"/>
+      <c r="P20" s="6">
+        <f>M20+N20-O20</f>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P18" xr:uid="{C08C8DD9-62BF-4F61-8FBF-6664D0041D04}">
-    <filterColumn colId="1" showButton="0"/>
-    <filterColumn colId="2" showButton="0"/>
-    <filterColumn colId="3" showButton="0"/>
-    <filterColumn colId="5" showButton="0"/>
-    <filterColumn colId="6" showButton="0"/>
-    <filterColumn colId="8" showButton="0"/>
-    <filterColumn colId="9" showButton="0"/>
+  <autoFilter ref="A3:P20" xr:uid="{C08C8DD9-62BF-4F61-8FBF-6664D0041D04}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:P20">
+      <sortCondition ref="B3:B20"/>
+    </sortState>
   </autoFilter>
   <mergeCells count="3">
     <mergeCell ref="B1:E1"/>
@@ -1426,6 +1450,7 @@
     <mergeCell ref="I1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1435,397 +1460,397 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="8" customWidth="1"/>
-    <col min="3" max="5" width="11.5546875" style="8"/>
-    <col min="6" max="6" width="49.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="7" customWidth="1"/>
+    <col min="3" max="5" width="11.5546875" style="7"/>
+    <col min="6" max="6" width="49.44140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="10">
+        <v>2675</v>
+      </c>
+      <c r="C2" s="10">
+        <v>50</v>
+      </c>
+      <c r="D2" s="10">
+        <v>20</v>
+      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="11">
-        <v>2675</v>
-      </c>
-      <c r="C2" s="11">
-        <v>50</v>
-      </c>
-      <c r="D2" s="11">
-        <v>20</v>
-      </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <v>70</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <f>B2-C2+D2-E2-G2</f>
         <v>2575</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="9">
+        <v>30</v>
+      </c>
+      <c r="B3" s="8">
         <v>300</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8">
         <v>119</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <f t="shared" ref="H3:H19" si="0">B3-C3+D3-E3-G3</f>
         <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="11">
+      <c r="A4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="10">
         <v>1000</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>80</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>140</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <v>250</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11">
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10">
         <f t="shared" si="0"/>
         <v>810</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="11">
+      <c r="A5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="10">
         <v>2152</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>60</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>95</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="E5" s="10"/>
+      <c r="F5" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="10">
         <v>33</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <f t="shared" si="0"/>
         <v>2154</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="11">
+      <c r="A6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="10">
         <v>164</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11">
+      <c r="C6" s="10"/>
+      <c r="D6" s="10">
         <v>50</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11">
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10">
         <v>3</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="10">
         <f t="shared" si="0"/>
         <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="11">
+      <c r="A7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="10">
         <v>2569</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11">
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10">
         <f t="shared" si="0"/>
         <v>2569</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="11">
+      <c r="A8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="10">
         <v>194</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>60</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11">
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10">
         <v>15</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="11">
+      <c r="A9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="10">
         <v>440</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10">
         <f t="shared" si="0"/>
         <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="11">
+      <c r="A10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="10">
         <v>1920</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11">
+      <c r="C10" s="10"/>
+      <c r="D10" s="10">
         <v>215</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <v>0</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="11">
+      <c r="F10" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="10">
         <v>14</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <f t="shared" si="0"/>
         <v>2121</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="11">
+      <c r="A11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="10">
         <v>759</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10">
         <f t="shared" si="0"/>
         <v>759</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="11">
+      <c r="A12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="10">
         <v>300</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11">
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="11">
+      <c r="A13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="10">
         <v>223</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11">
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10">
         <f t="shared" si="0"/>
         <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="11">
+      <c r="A14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="10">
         <v>12</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <v>45</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <v>40</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11">
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10">
         <v>18</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="10">
         <f t="shared" si="0"/>
         <v>-11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="11">
+      <c r="A15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="10">
         <v>280</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11">
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10">
         <f t="shared" si="0"/>
         <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="11">
+      <c r="A16" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="10">
         <v>300</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11">
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="9">
+        <v>26</v>
+      </c>
+      <c r="B17" s="8">
         <v>300</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9">
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="10">
+        <v>300</v>
+      </c>
+      <c r="C18" s="10">
+        <v>75</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10">
+        <v>0</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="11">
-        <v>300</v>
-      </c>
-      <c r="C18" s="11">
-        <v>75</v>
-      </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11">
-        <v>0</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="11">
+      <c r="G18" s="10">
         <v>88</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="10">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="11">
+      <c r="A19" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="10">
         <v>300</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>90</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11">
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
